--- a/result.xlsx
+++ b/result.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="96">
   <si>
     <t>受注日:</t>
   </si>
   <si>
-    <t>20260709</t>
+    <t>20260918</t>
   </si>
   <si>
     <t>顧客満足のため 受注チェックを確実に行います。</t>
@@ -88,22 +88,22 @@
     <t>Check</t>
   </si>
   <si>
-    <t>J607000580</t>
-  </si>
-  <si>
-    <t>2026/07/09</t>
-  </si>
-  <si>
-    <t>T0320</t>
+    <t>J609000731</t>
+  </si>
+  <si>
+    <t>2026/09/24</t>
+  </si>
+  <si>
+    <t>T0370</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>美野里真空株式会社</t>
-  </si>
-  <si>
-    <t>ＴＬ－４００ リターダー (15KG)</t>
+    <t>三栄産業株式会社</t>
+  </si>
+  <si>
+    <t>AS-5NP半艶消しｱﾝﾀﾞｰ(15KG)</t>
   </si>
   <si>
     <t>CN</t>
@@ -112,91 +112,75 @@
     <t>KG</t>
   </si>
   <si>
-    <t>2026/07/10</t>
+    <t>営業持参</t>
+  </si>
+  <si>
+    <t>納期遅延!
+2026/09/18?</t>
+  </si>
+  <si>
+    <t>ST-32NPA(改)ｸﾛｰﾑC001(15KG)</t>
+  </si>
+  <si>
+    <t>J609000732</t>
+  </si>
+  <si>
+    <t>2026/09/25</t>
+  </si>
+  <si>
+    <t>T0361</t>
+  </si>
+  <si>
+    <t>株式会社　光輝社　焼津製作所</t>
+  </si>
+  <si>
+    <t>ＰＩ－５０１不粘着化剤(18KG)</t>
+  </si>
+  <si>
+    <t>メーカー直送</t>
+  </si>
+  <si>
+    <t>納期遅延!
+2026/09/24?</t>
+  </si>
+  <si>
+    <t>J609000733</t>
   </si>
   <si>
     <t>レ</t>
   </si>
   <si>
-    <t>ＵＶ－５４２ アンダー (15KG)</t>
-  </si>
-  <si>
-    <t>J607000581</t>
-  </si>
-  <si>
-    <t>T0060</t>
-  </si>
-  <si>
-    <t>H006</t>
-  </si>
-  <si>
-    <t>伊坂化成株式会社　藤枝</t>
-  </si>
-  <si>
-    <t>有限会社　吉田技研</t>
-  </si>
-  <si>
-    <t>ＦＰＡ用 添加剤 (900G)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>J607000582</t>
-  </si>
-  <si>
-    <t>J607000583</t>
-  </si>
-  <si>
-    <t>2026/07/15</t>
-  </si>
-  <si>
-    <t>T4140</t>
-  </si>
-  <si>
-    <t>津田工業株式会社　川里工場</t>
-  </si>
-  <si>
-    <t>ＡＰＪ－９５３１ (15KG)</t>
-  </si>
-  <si>
-    <t>2026/07/16</t>
-  </si>
-  <si>
-    <t>J607000598</t>
-  </si>
-  <si>
-    <t>2026/07/31</t>
-  </si>
-  <si>
-    <t>T3050</t>
-  </si>
-  <si>
-    <t>新潟三桂株式会社</t>
-  </si>
-  <si>
-    <t>Ｕ－１００ シンナー (15KG)</t>
-  </si>
-  <si>
-    <t>2026/08/03</t>
-  </si>
-  <si>
-    <t>ＦＧ－３０００アンダー (15KG)</t>
-  </si>
-  <si>
-    <t>ＲＴ－４５ トップ (14KG)</t>
-  </si>
-  <si>
-    <t>J607000599</t>
-  </si>
-  <si>
-    <t>2026/08/21</t>
-  </si>
-  <si>
-    <t>2026/08/25</t>
-  </si>
-  <si>
-    <t>J607000600</t>
+    <t>J609000740</t>
+  </si>
+  <si>
+    <t>T0410</t>
+  </si>
+  <si>
+    <t>有限会社　新正加工</t>
+  </si>
+  <si>
+    <t>ST-32NPA 金色 T-5 (15KG)</t>
+  </si>
+  <si>
+    <t>2026/09/28</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Ｋ－１５０ＮＰアンダー (18㍑)</t>
+  </si>
+  <si>
+    <t>ＦＰＡ－３(改)２アンダー (18㍑)</t>
+  </si>
+  <si>
+    <t>ＳＴ－３２ＮＰＡトップ (15KG)</t>
+  </si>
+  <si>
+    <t>ＰＰ－３３ＮＰアンダー　(15KG)</t>
+  </si>
+  <si>
+    <t>J609000741</t>
   </si>
   <si>
     <t>T0020</t>
@@ -205,70 +189,121 @@
     <t>旭真空株式会社</t>
   </si>
   <si>
-    <t>ST-32NPA(改)ﾌﾞﾙｰ(ﾌﾞﾙｰX)260707②(4KG)</t>
-  </si>
-  <si>
-    <t>大久保様</t>
-  </si>
-  <si>
-    <t>ST-32NPA(改)ﾌﾞﾙｰ(ﾌﾞﾙｰX)260707①(4KG)</t>
-  </si>
-  <si>
-    <t>J607000603</t>
-  </si>
-  <si>
-    <t>染料液ブラック　(14KG)</t>
-  </si>
-  <si>
-    <t>2026/07/13</t>
-  </si>
-  <si>
-    <t>ＵＶ－２７０ＭＫ　アンダー(15KG)</t>
-  </si>
-  <si>
-    <t>J607000605</t>
-  </si>
-  <si>
-    <t>ST-32NPA(改) 金色Y003 (15KG)</t>
-  </si>
-  <si>
-    <t>2026/07/14</t>
-  </si>
-  <si>
-    <t>J607000609</t>
-  </si>
-  <si>
-    <t>T0370</t>
-  </si>
-  <si>
-    <t>三栄産業株式会社</t>
-  </si>
-  <si>
-    <t>ＦＰＡ－３(改)２ＨＮＶＤ５ｱﾝﾀﾞｰ (14.5KG)</t>
-  </si>
-  <si>
-    <t>J607000610</t>
-  </si>
-  <si>
-    <t>T3500</t>
-  </si>
-  <si>
-    <t>H189</t>
-  </si>
-  <si>
-    <t>高圧化工株式会社　千葉工場</t>
-  </si>
-  <si>
-    <t>株式会社　マスニ</t>
-  </si>
-  <si>
-    <t>ＵＶＺ－０５ アンダー (15KG)</t>
-  </si>
-  <si>
-    <t>J607000611</t>
-  </si>
-  <si>
-    <t>ＰＪ－Ｄ３ (15KG)</t>
+    <t>ＵⅤ－３６１Ｓアンダー (15KG)</t>
+  </si>
+  <si>
+    <t>J609000742</t>
+  </si>
+  <si>
+    <t>2026/10/06</t>
+  </si>
+  <si>
+    <t>T1210</t>
+  </si>
+  <si>
+    <t>GZK03</t>
+  </si>
+  <si>
+    <t>GZK_広州小糸</t>
+  </si>
+  <si>
+    <t>豊通ケミプラス株式会社　浜松営業所</t>
+  </si>
+  <si>
+    <t>安達包運倉庫株式会社</t>
+  </si>
+  <si>
+    <t>FK-13SHNV アンダー(UN/15KG)</t>
+  </si>
+  <si>
+    <t>2026/10/07</t>
+  </si>
+  <si>
+    <t>J609000743</t>
+  </si>
+  <si>
+    <t>2026/09/30</t>
+  </si>
+  <si>
+    <t>PHH04</t>
+  </si>
+  <si>
+    <t>ﾌｨﾘﾋﾟﾝﾍﾗｰ</t>
+  </si>
+  <si>
+    <t>ＳＴＲ－１２０ (UN/15KG)</t>
+  </si>
+  <si>
+    <t>2026/10/01</t>
+  </si>
+  <si>
+    <t>J609000744</t>
+  </si>
+  <si>
+    <t>THS01</t>
+  </si>
+  <si>
+    <t>THS_ﾀｲｽﾀﾝﾚｰ</t>
+  </si>
+  <si>
+    <t>名港海運㈱　西２区名港物流ｾﾝﾀｰ</t>
+  </si>
+  <si>
+    <t>ＳＲ－００１ Ａ (UN/15KG)</t>
+  </si>
+  <si>
+    <t>2026/10/02</t>
+  </si>
+  <si>
+    <t>ＳＲ－００１ Ｂ (UN/15KG)</t>
+  </si>
+  <si>
+    <t>ＳＵ－１００ＨＮＶ Ａ２ (UN/15KG)</t>
+  </si>
+  <si>
+    <t>ＳＵ－１００ＨＮＶ Ｂ (UN/15KG)</t>
+  </si>
+  <si>
+    <t>J609000745</t>
+  </si>
+  <si>
+    <t>2026/10/26</t>
+  </si>
+  <si>
+    <t>ＳＴＭ－３０－Ｔ１　(UN/15KG)</t>
+  </si>
+  <si>
+    <t>2026/10/27</t>
+  </si>
+  <si>
+    <t>J609000746</t>
+  </si>
+  <si>
+    <t>2026/10/28</t>
+  </si>
+  <si>
+    <t>INS11</t>
+  </si>
+  <si>
+    <t>INS_ｲﾝﾄﾞﾈｼｱｽﾀﾝﾚｰ</t>
+  </si>
+  <si>
+    <t>ＳＴＭ－４０－Ｔ１クリヤー (UN/15KG)</t>
+  </si>
+  <si>
+    <t>2026/10/29</t>
+  </si>
+  <si>
+    <t>J609000747</t>
+  </si>
+  <si>
+    <t>INK02</t>
+  </si>
+  <si>
+    <t>INK_ｲﾝﾄﾞﾈｼｱ小糸</t>
+  </si>
+  <si>
+    <t>ＰＲ－Ａ（ＫＡI） (UN/15KG)</t>
   </si>
 </sst>
 </file>
@@ -651,7 +686,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -746,7 +781,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" ht="30" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>24</v>
       </c>
@@ -773,28 +808,28 @@
         <v>29</v>
       </c>
       <c r="J4" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L4" s="4">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q4" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" s="4">
         <v>0</v>
@@ -803,7 +838,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
@@ -830,28 +865,28 @@
         <v>34</v>
       </c>
       <c r="J5" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="4">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q5" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" s="4">
         <v>0</v>
@@ -860,61 +895,61 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J6" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L6" s="4">
-        <v>0.9</v>
+        <v>72</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>1</v>
-      </c>
-      <c r="R6" s="4">
-        <v>45</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -925,32 +960,32 @@
         <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J7" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L7" s="4">
-        <v>0.9</v>
+        <v>225</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>31</v>
@@ -959,7 +994,7 @@
         <v>27</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>27</v>
@@ -971,43 +1006,43 @@
         <v>0</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J8" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L8" s="4">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>31</v>
@@ -1016,7 +1051,7 @@
         <v>27</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="P8" s="4" t="s">
         <v>27</v>
@@ -1028,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J9" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L9" s="4">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>31</v>
@@ -1073,55 +1108,55 @@
         <v>27</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="Q9" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R9" s="4">
         <v>0</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J10" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="4">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>31</v>
@@ -1130,55 +1165,55 @@
         <v>27</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="Q10" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R10" s="4">
         <v>0</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J11" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L11" s="4">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>31</v>
@@ -1187,55 +1222,55 @@
         <v>27</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="Q11" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R11" s="4">
         <v>0</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="J12" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L12" s="4">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>31</v>
@@ -1244,55 +1279,55 @@
         <v>27</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="Q12" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R12" s="4">
         <v>0</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J13" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L13" s="4">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>31</v>
@@ -1301,64 +1336,64 @@
         <v>27</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="Q13" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R13" s="4">
         <v>0</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J14" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L14" s="4">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>27</v>
@@ -1370,28 +1405,30 @@
         <v>0</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="F15" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>27</v>
@@ -1400,22 +1437,22 @@
         <v>65</v>
       </c>
       <c r="J15" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L15" s="4">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="P15" s="4" t="s">
         <v>27</v>
@@ -1427,43 +1464,45 @@
         <v>0</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="F16" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J16" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L16" s="4">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>31</v>
@@ -1472,7 +1511,7 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="P16" s="4" t="s">
         <v>27</v>
@@ -1484,43 +1523,45 @@
         <v>0</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F17" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J17" s="4">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L17" s="4">
-        <v>525</v>
+        <v>165</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>31</v>
@@ -1529,7 +1570,7 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P17" s="4" t="s">
         <v>27</v>
@@ -1541,43 +1582,45 @@
         <v>0</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F18" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J18" s="4">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L18" s="4">
-        <v>450</v>
+        <v>165</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>31</v>
@@ -1586,7 +1629,7 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P18" s="4" t="s">
         <v>27</v>
@@ -1598,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -1606,35 +1649,37 @@
         <v>73</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F19" s="4" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J19" s="4">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L19" s="4">
-        <v>43.5</v>
+        <v>630</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>31</v>
@@ -1643,7 +1688,7 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P19" s="4" t="s">
         <v>27</v>
@@ -1655,43 +1700,45 @@
         <v>0</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F20" s="4" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="J20" s="4">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L20" s="4">
-        <v>90</v>
+        <v>285</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>31</v>
@@ -1700,7 +1747,7 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P20" s="4" t="s">
         <v>27</v>
@@ -1712,28 +1759,30 @@
         <v>0</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="C21" s="4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="F21" s="4" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>27</v>
@@ -1742,13 +1791,13 @@
         <v>84</v>
       </c>
       <c r="J21" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L21" s="4">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>31</v>
@@ -1757,7 +1806,7 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="P21" s="4" t="s">
         <v>27</v>
@@ -1769,7 +1818,125 @@
         <v>0</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J22" s="4">
+        <v>1</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" s="4">
+        <v>15</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" s="4">
+        <v>44</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="4">
+        <v>660</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>0</v>
+      </c>
+      <c r="R23" s="4">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/result.xlsx
+++ b/result.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="72">
   <si>
     <t>受注日:</t>
   </si>
   <si>
-    <t>20260918</t>
+    <t>20261006</t>
   </si>
   <si>
     <t>顧客満足のため 受注チェックを確実に行います。</t>
@@ -28,7 +28,7 @@
     <t>担当者:</t>
   </si>
   <si>
-    <t>松戸</t>
+    <t>澤</t>
   </si>
   <si>
     <t>受注No</t>
@@ -88,22 +88,22 @@
     <t>Check</t>
   </si>
   <si>
-    <t>J609000731</t>
-  </si>
-  <si>
-    <t>2026/09/24</t>
-  </si>
-  <si>
-    <t>T0370</t>
+    <t>J610000533</t>
+  </si>
+  <si>
+    <t>2026/10/21</t>
+  </si>
+  <si>
+    <t>T0060</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>三栄産業株式会社</t>
-  </si>
-  <si>
-    <t>AS-5NP半艶消しｱﾝﾀﾞｰ(15KG)</t>
+    <t>伊坂化成株式会社　藤枝</t>
+  </si>
+  <si>
+    <t>ＲＴＳ－０４アンダー (15KG)</t>
   </si>
   <si>
     <t>CN</t>
@@ -112,45 +112,88 @@
     <t>KG</t>
   </si>
   <si>
-    <t>営業持参</t>
-  </si>
-  <si>
-    <t>納期遅延!
-2026/09/18?</t>
-  </si>
-  <si>
-    <t>ST-32NPA(改)ｸﾛｰﾑC001(15KG)</t>
-  </si>
-  <si>
-    <t>J609000732</t>
-  </si>
-  <si>
-    <t>2026/09/25</t>
-  </si>
-  <si>
-    <t>T0361</t>
-  </si>
-  <si>
-    <t>株式会社　光輝社　焼津製作所</t>
-  </si>
-  <si>
-    <t>ＰＩ－５０１不粘着化剤(18KG)</t>
-  </si>
-  <si>
-    <t>メーカー直送</t>
-  </si>
-  <si>
-    <t>納期遅延!
-2026/09/24?</t>
-  </si>
-  <si>
-    <t>J609000733</t>
+    <t>2026/10/22</t>
   </si>
   <si>
     <t>レ</t>
   </si>
   <si>
-    <t>J609000740</t>
+    <t>2026/11/04</t>
+  </si>
+  <si>
+    <t>2026/11/05</t>
+  </si>
+  <si>
+    <t>ＵＶ－９０６アンダー (15Kg)</t>
+  </si>
+  <si>
+    <t>J610000534</t>
+  </si>
+  <si>
+    <t>2026/10/08</t>
+  </si>
+  <si>
+    <t>T0020</t>
+  </si>
+  <si>
+    <t>旭真空株式会社</t>
+  </si>
+  <si>
+    <t>ＵＶ－２７０ＭＫ　アンダー(15KG)</t>
+  </si>
+  <si>
+    <t>2026/10/09</t>
+  </si>
+  <si>
+    <t>J610000537</t>
+  </si>
+  <si>
+    <t>2026/11/13</t>
+  </si>
+  <si>
+    <t>T1210</t>
+  </si>
+  <si>
+    <t>H153</t>
+  </si>
+  <si>
+    <t>豊通ケミプラス株式会社　浜松営業所</t>
+  </si>
+  <si>
+    <t>株式会社　タキ倉庫　榛南営業所</t>
+  </si>
+  <si>
+    <t>ＰＲ－Ａ(改） (15KG)</t>
+  </si>
+  <si>
+    <t>2026/11/16</t>
+  </si>
+  <si>
+    <t>J610000540</t>
+  </si>
+  <si>
+    <t>T3570</t>
+  </si>
+  <si>
+    <t>H224</t>
+  </si>
+  <si>
+    <t>株式会社　トウ・プラス　寺尾工場</t>
+  </si>
+  <si>
+    <t>株式会社　トウ・プラス　小鹿野工場</t>
+  </si>
+  <si>
+    <t>ガンクリーナーＡ (16㍑）</t>
+  </si>
+  <si>
+    <t>2026/10/13</t>
+  </si>
+  <si>
+    <t>J610000541</t>
+  </si>
+  <si>
+    <t>2026/10/07</t>
   </si>
   <si>
     <t>T0410</t>
@@ -159,151 +202,35 @@
     <t>有限会社　新正加工</t>
   </si>
   <si>
+    <t>ＦＰＡ－３(改)２アンダー (18㍑)</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>レ
+!東洋運賃を確認してください</t>
+  </si>
+  <si>
     <t>ST-32NPA 金色 T-5 (15KG)</t>
   </si>
   <si>
-    <t>2026/09/28</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Ｋ－１５０ＮＰアンダー (18㍑)</t>
-  </si>
-  <si>
-    <t>ＦＰＡ－３(改)２アンダー (18㍑)</t>
-  </si>
-  <si>
     <t>ＳＴ－３２ＮＰＡトップ (15KG)</t>
   </si>
   <si>
-    <t>ＰＰ－３３ＮＰアンダー　(15KG)</t>
-  </si>
-  <si>
-    <t>J609000741</t>
-  </si>
-  <si>
-    <t>T0020</t>
-  </si>
-  <si>
-    <t>旭真空株式会社</t>
-  </si>
-  <si>
-    <t>ＵⅤ－３６１Ｓアンダー (15KG)</t>
-  </si>
-  <si>
-    <t>J609000742</t>
-  </si>
-  <si>
-    <t>2026/10/06</t>
-  </si>
-  <si>
-    <t>T1210</t>
-  </si>
-  <si>
-    <t>GZK03</t>
-  </si>
-  <si>
-    <t>GZK_広州小糸</t>
-  </si>
-  <si>
-    <t>豊通ケミプラス株式会社　浜松営業所</t>
-  </si>
-  <si>
-    <t>安達包運倉庫株式会社</t>
-  </si>
-  <si>
-    <t>FK-13SHNV アンダー(UN/15KG)</t>
-  </si>
-  <si>
-    <t>2026/10/07</t>
-  </si>
-  <si>
-    <t>J609000743</t>
-  </si>
-  <si>
-    <t>2026/09/30</t>
-  </si>
-  <si>
-    <t>PHH04</t>
-  </si>
-  <si>
-    <t>ﾌｨﾘﾋﾟﾝﾍﾗｰ</t>
-  </si>
-  <si>
-    <t>ＳＴＲ－１２０ (UN/15KG)</t>
-  </si>
-  <si>
-    <t>2026/10/01</t>
-  </si>
-  <si>
-    <t>J609000744</t>
-  </si>
-  <si>
-    <t>THS01</t>
-  </si>
-  <si>
-    <t>THS_ﾀｲｽﾀﾝﾚｰ</t>
-  </si>
-  <si>
-    <t>名港海運㈱　西２区名港物流ｾﾝﾀｰ</t>
-  </si>
-  <si>
-    <t>ＳＲ－００１ Ａ (UN/15KG)</t>
-  </si>
-  <si>
-    <t>2026/10/02</t>
-  </si>
-  <si>
-    <t>ＳＲ－００１ Ｂ (UN/15KG)</t>
-  </si>
-  <si>
-    <t>ＳＵ－１００ＨＮＶ Ａ２ (UN/15KG)</t>
-  </si>
-  <si>
-    <t>ＳＵ－１００ＨＮＶ Ｂ (UN/15KG)</t>
-  </si>
-  <si>
-    <t>J609000745</t>
-  </si>
-  <si>
-    <t>2026/10/26</t>
-  </si>
-  <si>
-    <t>ＳＴＭ－３０－Ｔ１　(UN/15KG)</t>
-  </si>
-  <si>
-    <t>2026/10/27</t>
-  </si>
-  <si>
-    <t>J609000746</t>
-  </si>
-  <si>
-    <t>2026/10/28</t>
-  </si>
-  <si>
-    <t>INS11</t>
-  </si>
-  <si>
-    <t>INS_ｲﾝﾄﾞﾈｼｱｽﾀﾝﾚｰ</t>
-  </si>
-  <si>
-    <t>ＳＴＭ－４０－Ｔ１クリヤー (UN/15KG)</t>
-  </si>
-  <si>
-    <t>2026/10/29</t>
-  </si>
-  <si>
-    <t>J609000747</t>
-  </si>
-  <si>
-    <t>INK02</t>
-  </si>
-  <si>
-    <t>INK_ｲﾝﾄﾞﾈｼｱ小糸</t>
-  </si>
-  <si>
-    <t>ＰＲ－Ａ（ＫＡI） (UN/15KG)</t>
+    <t>J610000542</t>
+  </si>
+  <si>
+    <t>T4230</t>
+  </si>
+  <si>
+    <t>H251</t>
+  </si>
+  <si>
+    <t>株式会社　エイアイエム　群馬工場</t>
+  </si>
+  <si>
+    <t>ディアンドディ株式会社</t>
   </si>
 </sst>
 </file>
@@ -686,7 +613,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -781,7 +708,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30" customHeight="1">
+    <row r="4" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>24</v>
       </c>
@@ -808,22 +735,22 @@
         <v>29</v>
       </c>
       <c r="J4" s="4">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L4" s="4">
-        <v>150</v>
+        <v>960</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>27</v>
@@ -838,12 +765,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="30" customHeight="1">
+    <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>26</v>
@@ -862,25 +789,25 @@
         <v>27</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J5" s="4">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="4">
-        <v>75</v>
+        <v>960</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>27</v>
@@ -895,49 +822,49 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" customHeight="1">
+    <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J6" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L6" s="4">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>27</v>
@@ -949,43 +876,43 @@
         <v>0</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J7" s="4">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L7" s="4">
-        <v>225</v>
+        <v>525</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>31</v>
@@ -994,7 +921,7 @@
         <v>27</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>27</v>
@@ -1006,43 +933,43 @@
         <v>0</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="J8" s="4">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L8" s="4">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>31</v>
@@ -1051,7 +978,7 @@
         <v>27</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="P8" s="4" t="s">
         <v>27</v>
@@ -1063,43 +990,43 @@
         <v>0</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J9" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L9" s="4">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>31</v>
@@ -1108,55 +1035,55 @@
         <v>27</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="Q9" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R9" s="4">
         <v>0</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J10" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="4">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>31</v>
@@ -1165,55 +1092,55 @@
         <v>27</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="Q10" s="4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R10" s="4">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="J11" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L11" s="4">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>31</v>
@@ -1222,55 +1149,55 @@
         <v>27</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="Q11" s="4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R11" s="4">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="J12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L12" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>31</v>
@@ -1279,55 +1206,55 @@
         <v>27</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R12" s="4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="4" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J13" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L13" s="4">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>31</v>
@@ -1336,607 +1263,19 @@
         <v>27</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="Q13" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R13" s="4">
         <v>0</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
-      <c r="A14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" s="4">
-        <v>3</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="4">
-        <v>45</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4">
-        <v>0</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
-      <c r="A15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J15" s="4">
-        <v>3</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="4">
-        <v>45</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>0</v>
-      </c>
-      <c r="R15" s="4">
-        <v>0</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="4">
-        <v>4</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="4">
-        <v>60</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q16" s="4">
-        <v>0</v>
-      </c>
-      <c r="R16" s="4">
-        <v>0</v>
-      </c>
-      <c r="S16" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J17" s="4">
-        <v>11</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" s="4">
-        <v>165</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>0</v>
-      </c>
-      <c r="R17" s="4">
-        <v>0</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
-      <c r="A18" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="J18" s="4">
-        <v>11</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="4">
-        <v>165</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q18" s="4">
-        <v>0</v>
-      </c>
-      <c r="R18" s="4">
-        <v>0</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
-      <c r="A19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J19" s="4">
-        <v>42</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="4">
-        <v>630</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q19" s="4">
-        <v>0</v>
-      </c>
-      <c r="R19" s="4">
-        <v>0</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
-      <c r="A20" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J20" s="4">
-        <v>19</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="4">
-        <v>285</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="4">
-        <v>0</v>
-      </c>
-      <c r="R20" s="4">
-        <v>0</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19">
-      <c r="A21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J21" s="4">
-        <v>8</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" s="4">
-        <v>120</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q21" s="4">
-        <v>0</v>
-      </c>
-      <c r="R21" s="4">
-        <v>0</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
-      <c r="A22" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="J22" s="4">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L22" s="4">
-        <v>15</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>0</v>
-      </c>
-      <c r="R22" s="4">
-        <v>0</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
-      <c r="A23" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J23" s="4">
-        <v>44</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" s="4">
-        <v>660</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" s="4">
-        <v>0</v>
-      </c>
-      <c r="R23" s="4">
-        <v>0</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/result.xlsx
+++ b/result.xlsx
@@ -209,7 +209,7 @@
   </si>
   <si>
     <t>レ
-!東洋運賃を確認してください</t>
+東洋運賃を確認してください</t>
   </si>
   <si>
     <t>ST-32NPA 金色 T-5 (15KG)</t>
@@ -1101,7 +1101,7 @@
         <v>7</v>
       </c>
       <c r="R10" s="4">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="S10" s="4" t="s">
         <v>64</v>
@@ -1158,7 +1158,7 @@
         <v>7</v>
       </c>
       <c r="R11" s="4">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="S11" s="4" t="s">
         <v>64</v>
@@ -1215,7 +1215,7 @@
         <v>7</v>
       </c>
       <c r="R12" s="4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="S12" s="4" t="s">
         <v>64</v>
